--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89279CDE-FC68-4D67-9B26-6B5E72393BEE}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E7B5833-9B06-4E8B-B4BD-8F104E9E55ED}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5224" uniqueCount="2661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5227" uniqueCount="2663">
   <si>
     <t>type</t>
   </si>
@@ -8022,16 +8022,28 @@
   </si>
   <si>
     <t>3rd</t>
+  </si>
+  <si>
+    <t>BRA GABRIEL - 3</t>
+  </si>
+  <si>
+    <t>finalgroup</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -28485,6 +28497,9 @@
       <c r="A6" t="s">
         <v>2557</v>
       </c>
+      <c r="B6" t="s">
+        <v>2662</v>
+      </c>
       <c r="M6" t="s">
         <v>2642</v>
       </c>
@@ -28580,6 +28595,9 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2558</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2662</v>
       </c>
     </row>
   </sheetData>
@@ -31464,8 +31482,8 @@
       <c r="B160" t="s">
         <v>178</v>
       </c>
-      <c r="C160" t="e">
-        <v>#NAME?</v>
+      <c r="C160" t="s">
+        <v>2661</v>
       </c>
       <c r="D160" t="s">
         <v>176</v>
@@ -51716,6 +51734,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF69802-4C43-4E10-B31D-E050D540A4BD}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A97ACB7-CA6F-46BD-A86B-EDB89F623B00}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5221" uniqueCount="2658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="2658">
   <si>
     <t>type</t>
   </si>
@@ -51178,6 +51178,9 @@
       <c r="C1258" t="s">
         <v>2565</v>
       </c>
+      <c r="D1258" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="1259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1259" t="s">
@@ -51189,6 +51192,9 @@
       <c r="C1259" t="s">
         <v>2566</v>
       </c>
+      <c r="D1259" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="1260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1260" t="s">
@@ -51200,6 +51206,9 @@
       <c r="C1260" t="s">
         <v>2567</v>
       </c>
+      <c r="D1260" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="1261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1261" t="s">
@@ -51211,6 +51220,9 @@
       <c r="C1261" t="s">
         <v>2568</v>
       </c>
+      <c r="D1261" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="1262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1262" t="s">
@@ -51222,6 +51234,9 @@
       <c r="C1262" t="s">
         <v>2569</v>
       </c>
+      <c r="D1262" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="1263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1263" t="s">
@@ -51233,6 +51248,9 @@
       <c r="C1263" t="s">
         <v>2570</v>
       </c>
+      <c r="D1263" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="1264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1264" t="s">
@@ -51244,8 +51262,11 @@
       <c r="C1264" t="s">
         <v>2571</v>
       </c>
-    </row>
-    <row r="1265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1264" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1265" t="s">
         <v>2612</v>
       </c>
@@ -51255,8 +51276,11 @@
       <c r="C1265" t="s">
         <v>2572</v>
       </c>
-    </row>
-    <row r="1266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1265" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1266" t="s">
         <v>2612</v>
       </c>
@@ -51266,8 +51290,11 @@
       <c r="C1266" t="s">
         <v>2573</v>
       </c>
-    </row>
-    <row r="1267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1266" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1267" t="s">
         <v>2612</v>
       </c>
@@ -51277,8 +51304,11 @@
       <c r="C1267" t="s">
         <v>2574</v>
       </c>
-    </row>
-    <row r="1268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1267" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1268" t="s">
         <v>2612</v>
       </c>
@@ -51288,8 +51318,11 @@
       <c r="C1268" t="s">
         <v>2575</v>
       </c>
-    </row>
-    <row r="1269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1268" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1269" t="s">
         <v>2612</v>
       </c>
@@ -51299,8 +51332,11 @@
       <c r="C1269" t="s">
         <v>2576</v>
       </c>
-    </row>
-    <row r="1270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1269" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1270" t="s">
         <v>2612</v>
       </c>
@@ -51310,8 +51346,11 @@
       <c r="C1270" t="s">
         <v>2577</v>
       </c>
-    </row>
-    <row r="1271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1270" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1271" t="s">
         <v>2612</v>
       </c>
@@ -51321,8 +51360,11 @@
       <c r="C1271" t="s">
         <v>2578</v>
       </c>
-    </row>
-    <row r="1272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1271" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1272" t="s">
         <v>2612</v>
       </c>
@@ -51332,8 +51374,11 @@
       <c r="C1272" t="s">
         <v>2579</v>
       </c>
-    </row>
-    <row r="1273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1272" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1273" t="s">
         <v>2612</v>
       </c>
@@ -51343,8 +51388,11 @@
       <c r="C1273" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="1274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1273" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1274" t="s">
         <v>2612</v>
       </c>
@@ -51354,8 +51402,11 @@
       <c r="C1274" t="s">
         <v>2580</v>
       </c>
-    </row>
-    <row r="1275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1274" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1275" t="s">
         <v>2612</v>
       </c>
@@ -51365,8 +51416,11 @@
       <c r="C1275" t="s">
         <v>2581</v>
       </c>
-    </row>
-    <row r="1276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1275" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1276" t="s">
         <v>2612</v>
       </c>
@@ -51376,8 +51430,11 @@
       <c r="C1276" t="s">
         <v>2582</v>
       </c>
-    </row>
-    <row r="1277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1276" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1277" t="s">
         <v>2612</v>
       </c>
@@ -51387,8 +51444,11 @@
       <c r="C1277" t="s">
         <v>2583</v>
       </c>
-    </row>
-    <row r="1278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1277" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1278" t="s">
         <v>2612</v>
       </c>
@@ -51398,8 +51458,11 @@
       <c r="C1278" t="s">
         <v>2584</v>
       </c>
-    </row>
-    <row r="1279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1278" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1279" t="s">
         <v>2612</v>
       </c>
@@ -51409,8 +51472,11 @@
       <c r="C1279" t="s">
         <v>2585</v>
       </c>
-    </row>
-    <row r="1280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1279" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1280" t="s">
         <v>2612</v>
       </c>
@@ -51420,8 +51486,11 @@
       <c r="C1280" t="s">
         <v>2586</v>
       </c>
-    </row>
-    <row r="1281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1280" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1281" t="s">
         <v>2612</v>
       </c>
@@ -51431,8 +51500,11 @@
       <c r="C1281" t="s">
         <v>2587</v>
       </c>
-    </row>
-    <row r="1282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1281" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1282" t="s">
         <v>2612</v>
       </c>
@@ -51442,8 +51514,11 @@
       <c r="C1282" t="s">
         <v>2588</v>
       </c>
-    </row>
-    <row r="1283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1282" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1283" t="s">
         <v>2612</v>
       </c>
@@ -51453,8 +51528,11 @@
       <c r="C1283" t="s">
         <v>2589</v>
       </c>
-    </row>
-    <row r="1284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1283" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1284" t="s">
         <v>2612</v>
       </c>
@@ -51464,8 +51542,11 @@
       <c r="C1284" t="s">
         <v>2590</v>
       </c>
-    </row>
-    <row r="1285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1284" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1285" t="s">
         <v>2612</v>
       </c>
@@ -51475,8 +51556,11 @@
       <c r="C1285" t="s">
         <v>2591</v>
       </c>
-    </row>
-    <row r="1286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1285" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1286" t="s">
         <v>2612</v>
       </c>
@@ -51486,8 +51570,11 @@
       <c r="C1286" t="s">
         <v>2592</v>
       </c>
-    </row>
-    <row r="1287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1286" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1287" t="s">
         <v>2612</v>
       </c>
@@ -51497,8 +51584,11 @@
       <c r="C1287" t="s">
         <v>2593</v>
       </c>
-    </row>
-    <row r="1288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1287" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1288" t="s">
         <v>2612</v>
       </c>
@@ -51508,8 +51598,11 @@
       <c r="C1288" t="s">
         <v>2594</v>
       </c>
-    </row>
-    <row r="1289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1288" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1289" t="s">
         <v>2612</v>
       </c>
@@ -51519,8 +51612,11 @@
       <c r="C1289" t="s">
         <v>2595</v>
       </c>
-    </row>
-    <row r="1290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1289" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1290" t="s">
         <v>2612</v>
       </c>
@@ -51530,8 +51626,11 @@
       <c r="C1290" t="s">
         <v>2596</v>
       </c>
-    </row>
-    <row r="1291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1290" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1291" t="s">
         <v>2612</v>
       </c>
@@ -51541,8 +51640,11 @@
       <c r="C1291" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="1292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1291" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1292" t="s">
         <v>2612</v>
       </c>
@@ -51552,8 +51654,11 @@
       <c r="C1292" t="s">
         <v>2598</v>
       </c>
-    </row>
-    <row r="1293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1292" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1293" t="s">
         <v>2612</v>
       </c>
@@ -51563,8 +51668,11 @@
       <c r="C1293" t="s">
         <v>2599</v>
       </c>
-    </row>
-    <row r="1294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1293" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1294" t="s">
         <v>2612</v>
       </c>
@@ -51574,8 +51682,11 @@
       <c r="C1294" t="s">
         <v>2600</v>
       </c>
-    </row>
-    <row r="1295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1294" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1295" t="s">
         <v>2612</v>
       </c>
@@ -51585,8 +51696,11 @@
       <c r="C1295" t="s">
         <v>2601</v>
       </c>
-    </row>
-    <row r="1296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1295" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1296" t="s">
         <v>2612</v>
       </c>
@@ -51596,8 +51710,11 @@
       <c r="C1296" t="s">
         <v>2602</v>
       </c>
-    </row>
-    <row r="1297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1296" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1297" t="s">
         <v>2612</v>
       </c>
@@ -51607,8 +51724,11 @@
       <c r="C1297" t="s">
         <v>2603</v>
       </c>
-    </row>
-    <row r="1298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1297" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1298" t="s">
         <v>2612</v>
       </c>
@@ -51618,8 +51738,11 @@
       <c r="C1298" t="s">
         <v>2604</v>
       </c>
-    </row>
-    <row r="1299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1298" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1299" t="s">
         <v>2612</v>
       </c>
@@ -51629,8 +51752,11 @@
       <c r="C1299" t="s">
         <v>2605</v>
       </c>
-    </row>
-    <row r="1300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1299" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1300" t="s">
         <v>2612</v>
       </c>
@@ -51640,8 +51766,11 @@
       <c r="C1300" t="s">
         <v>2606</v>
       </c>
-    </row>
-    <row r="1301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1300" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1301" t="s">
         <v>2612</v>
       </c>
@@ -51651,8 +51780,11 @@
       <c r="C1301" t="s">
         <v>2607</v>
       </c>
-    </row>
-    <row r="1302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1301" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1302" t="s">
         <v>2612</v>
       </c>
@@ -51662,8 +51794,11 @@
       <c r="C1302" t="s">
         <v>2608</v>
       </c>
-    </row>
-    <row r="1303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1302" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1303" t="s">
         <v>2612</v>
       </c>
@@ -51673,8 +51808,11 @@
       <c r="C1303" t="s">
         <v>2609</v>
       </c>
-    </row>
-    <row r="1304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1303" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1304" t="s">
         <v>2612</v>
       </c>
@@ -51684,8 +51822,11 @@
       <c r="C1304" t="s">
         <v>2610</v>
       </c>
-    </row>
-    <row r="1305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1304" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1305" t="s">
         <v>2612</v>
       </c>
@@ -51694,6 +51835,9 @@
       </c>
       <c r="C1305" t="s">
         <v>2611</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A97ACB7-CA6F-46BD-A86B-EDB89F623B00}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8838C9-C72B-4A0B-96BB-2AF7B775E490}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -8006,13 +8006,13 @@
     <t>ENG CHALOBAH - 12</t>
   </si>
   <si>
-    <t>3rd</t>
-  </si>
-  <si>
     <t>BRA GABRIEL - 3</t>
   </si>
   <si>
     <t>finalgroup</t>
+  </si>
+  <si>
+    <t>r32</t>
   </si>
 </sst>
 </file>
@@ -28475,7 +28475,7 @@
         <v>1314</v>
       </c>
       <c r="F5" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -28483,7 +28483,7 @@
         <v>2552</v>
       </c>
       <c r="B6" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="M6" t="s">
         <v>2637</v>
@@ -28582,7 +28582,7 @@
         <v>2553</v>
       </c>
       <c r="B12" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
   </sheetData>
@@ -31468,7 +31468,7 @@
         <v>178</v>
       </c>
       <c r="C160" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="D160" t="s">
         <v>176</v>

--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EEFA7CF-6AAA-4958-AD7E-5893B006D93F}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4513467C-534A-47F8-ACE7-D7AAD1EB2D17}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -11518,7 +11518,7 @@
     <t>Can UZUN - Türkiye</t>
   </si>
   <si>
-    <t>r16</t>
+    <t>r4</t>
   </si>
 </sst>
 </file>

--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4513467C-534A-47F8-ACE7-D7AAD1EB2D17}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F2BBABA-DC73-4115-84C2-114F77A0E5D0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11518,7 +11518,7 @@
     <t>Can UZUN - Türkiye</t>
   </si>
   <si>
-    <t>r4</t>
+    <t>r2</t>
   </si>
 </sst>
 </file>

--- a/otherquest.xlsx
+++ b/otherquest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/francis_fayolle_undp_org/Documents/Documents/World-Cup-betting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F2BBABA-DC73-4115-84C2-114F77A0E5D0}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{4C985157-073D-4958-910F-2D539070ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8912848F-2D02-4302-A252-71D29CBA7549}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">choices!$A$1:$E$1149</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -11518,7 +11518,7 @@
     <t>Can UZUN - Türkiye</t>
   </si>
   <si>
-    <t>r2</t>
+    <t>r1</t>
   </si>
 </sst>
 </file>
